--- a/chinese_learning_streamlit (1).xlsx
+++ b/chinese_learning_streamlit (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\er5FILES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasee\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCC885B-B73F-4007-B611-57097C8A9273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B19F2D6F-B0A4-43E8-80BB-2DFBC39A9F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="16260" windowHeight="11508" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4940" uniqueCount="3299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4944" uniqueCount="3303">
   <si>
     <t>Category</t>
   </si>
@@ -9917,6 +9917,60 @@
   </si>
   <si>
     <t>Shǒu’ěr</t>
+  </si>
+  <si>
+    <t>路人：你需要我幫忙嗎？
+安同：我好像迷路了。
+路人：你要去哪裡？
+安同：請問，到師大怎麼走？
+路人：你從這裡往前走，到了下一個路口，右轉。
+安同：右轉就到了嗎？聽起來不遠。
+路人：還沒到！你右轉以後，是和平東路一段，再往前一直走，過了第二個紅綠燈，就看見師大了。
+安同：謝謝，我知道了。
+路人：你的中文很好。
+安同：謝謝，我還得多學一點。能不能再告訴我，這附近有沒有提款機？
+路人：從這裡往和平東路走，好像沒有銀行，不過大部分的超商裡應該都有。
+安同：你說的「超商」是「7-11」那種便利商店嗎？
+路人：是的。對了，郵局也可以提款。
+安同：我看見了，那邊有一家便利商店。謝謝，謝謝！
+路人：不客氣。</t>
+  </si>
+  <si>
+    <t>Lùrén: Nǐ xūyào wǒ bāngmáng ma?
+Ān Tóng: Wǒ hǎoxiàng mílù le.
+Lùrén: Nǐ yào qù nǎlǐ?
+Ān Tóng: Qǐngwèn, dào Shīdà zěnme zǒu?
+Lùrén: Nǐ cóng zhèlǐ wǎng qián zǒu, dào le xià yí gè lùkǒu, yòu zhuǎn.
+Ān Tóng: Yòu zhuǎn jiù dào le ma? Tīng qǐlái bù yuǎn.
+Lùrén: Hái méi dào! Nǐ yòu zhuǎn yǐhòu, shì Hépíng Dōng Lù Yí Duàn, zài wǎng qián yìzhí zǒu, guò le dì èr gè hónglǜdēng, jiù kànjiàn Shīdà le.
+Ān Tóng: Xièxiè, wǒ zhīdào le.
+Lùrén: Nǐ de Zhōngwén hěn hǎo.
+Ān Tóng: Xièxiè, wǒ hái děi duō xué yìdiǎn. Néng bu néng zài gàosu wǒ, zhè fùjìn yǒu méiyǒu tíkuǎnjī?
+Lùrén: Cóng zhèlǐ wǎng Hépíng Dōng Lù zǒu, hǎoxiàng méiyǒu yínháng, búguò dà bùfèn de chāoshāng lǐ yīnggāi dōu yǒu.
+Ān Tóng: Nǐ shuō de “chāoshāng” shì “7-11” nà zhǒng biànlì shāngdiàn ma?
+Lùrén: Shì de. Duì le, yóujú yě kěyǐ tíkuǎn.
+Ān Tóng: Wǒ kànjiàn le, nàbiān yǒu yì jiā biànlì shāngdiàn. Xièxiè, xièxiè!
+Lùrén: Bú kèqì.</t>
+  </si>
+  <si>
+    <t>Passerby: Do you need my help?
+Antong: I think I’m lost.
+Passerby: Where are you going?
+Antong: Excuse me, how do I get to Shida (NTNU)?
+Passerby: Go straight from here. When you reach the next intersection, turn right.
+Antong: If I turn right, will I arrive? It sounds close.
+Passerby: Not yet! After you turn right, that’s Section 1 of Heping East Road. Keep going straight. After the second traffic light, you’ll see Shida.
+Antong: Thank you, I understand.
+Passerby: Your Chinese is very good.
+Antong: Thanks, I still need to learn more. Could you also tell me if there is an ATM nearby?
+Passerby: If you walk toward Heping East Road from here, there doesn’t seem to be a bank, but most convenience stores should have one.
+Antong: By “convenience store,” do you mean stores like 7-11?
+Passerby: Yes. Also, the post office can provide withdrawals.
+Antong: I see it. There’s a convenience store over there. Thank you, thank you!
+Passerby: You’re welcome.</t>
+  </si>
+  <si>
+    <t>Textbook Study Map</t>
   </si>
 </sst>
 </file>
@@ -9975,13 +10029,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10287,7 +10344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1235"/>
+  <dimension ref="A1:D1236"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -13193,7 +13250,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>588</v>
       </c>
@@ -13207,7 +13264,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>588</v>
       </c>
@@ -13221,7 +13278,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>588</v>
       </c>
@@ -13263,7 +13320,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>588</v>
       </c>
@@ -13347,7 +13404,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>588</v>
       </c>
@@ -13473,7 +13530,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>588</v>
       </c>
@@ -13641,7 +13698,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>588</v>
       </c>
@@ -13655,7 +13712,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>588</v>
       </c>
@@ -13669,7 +13726,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>588</v>
       </c>
@@ -13683,7 +13740,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="243" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>588</v>
       </c>
@@ -13697,7 +13754,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>588</v>
       </c>
@@ -13725,7 +13782,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>588</v>
       </c>
@@ -13753,7 +13810,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>588</v>
       </c>
@@ -14145,7 +14202,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>588</v>
       </c>
@@ -14201,7 +14258,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="280" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>588</v>
       </c>
@@ -14215,7 +14272,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>588</v>
       </c>
@@ -14495,7 +14552,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>588</v>
       </c>
@@ -14607,7 +14664,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>588</v>
       </c>
@@ -14621,7 +14678,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="310" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>588</v>
       </c>
@@ -15097,7 +15154,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>588</v>
       </c>
@@ -15237,7 +15294,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>588</v>
       </c>
@@ -15293,7 +15350,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>588</v>
       </c>
@@ -15307,7 +15364,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>588</v>
       </c>
@@ -16329,7 +16386,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>588</v>
       </c>
@@ -16343,7 +16400,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>588</v>
       </c>
@@ -16469,7 +16526,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>588</v>
       </c>
@@ -16511,7 +16568,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>588</v>
       </c>
@@ -17127,7 +17184,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>588</v>
       </c>
@@ -17141,7 +17198,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>588</v>
       </c>
@@ -17155,7 +17212,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>588</v>
       </c>
@@ -17169,7 +17226,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="492" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
         <v>588</v>
       </c>
@@ -17183,7 +17240,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="493" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>588</v>
       </c>
@@ -27583,6 +27640,20 @@
       </c>
       <c r="D1235" t="s">
         <v>3298</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A1236" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1236" s="3" t="s">
+        <v>3301</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>3299</v>
+      </c>
+      <c r="D1236" s="3" t="s">
+        <v>3300</v>
       </c>
     </row>
   </sheetData>

--- a/chinese_learning_streamlit (1).xlsx
+++ b/chinese_learning_streamlit (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasee\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B19F2D6F-B0A4-43E8-80BB-2DFBC39A9F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A0321E-57F1-46CF-BDF4-9A06FFC8EFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9970,14 +9970,14 @@
 Passerby: You’re welcome.</t>
   </si>
   <si>
-    <t>Textbook Study Map</t>
+    <t>textbook entire study map</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9992,6 +9992,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF926C05"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -10029,7 +10035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -10040,6 +10046,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27643,7 +27650,7 @@
       </c>
     </row>
     <row r="1236" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A1236" t="s">
+      <c r="A1236" s="4" t="s">
         <v>3302</v>
       </c>
       <c r="B1236" s="3" t="s">

--- a/chinese_learning_streamlit (1).xlsx
+++ b/chinese_learning_streamlit (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasee\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wasee\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A0321E-57F1-46CF-BDF4-9A06FFC8EFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07EEEA33-3798-41E6-B793-C49461C63A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4944" uniqueCount="3303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5004" uniqueCount="3348">
   <si>
     <t>Category</t>
   </si>
@@ -9971,6 +9971,141 @@
   </si>
   <si>
     <t>textbook entire study map</t>
+  </si>
+  <si>
+    <t>Ma Antong downloaded a new map on his phone and asked Bai Ruyu to walk around near NTNU with him to test if the map was useful. They looked at the map, turned left from the school gate, and after passing Heping East Road, they arrived at Shida Road. On Shida Road, they saw many snack shops, as well as stores selling clothes and daily necessities. They passed two small alleys and then turned right; there were more shops here than on Shida Road. They walked for half a day, and Bai Ruyu felt a little hungry, so they went to a noodle shop and ordered two bowls of beef noodles. While eating, they looked at the map on the phone and found that in a nearby alley there was a shop selling backpacks. Ma Antong happened to want to buy a backpack, so they decided to go check it out after eating. In the end, Ma Antong bought a backpack, and Bai Ruyu also bought two pens and a notebook nearby. Both of them felt that the shops near NTNU were very interesting, and the food and daily necessities were also very affordable.</t>
+  </si>
+  <si>
+    <t>馬安同下載了新的地圖到手機裡，他找白如玉跟他在師大附近走走，試試地圖好用不好用。他們看著地圖，從學校門口往左轉，過了和平東路就到了師大路。在師大路上，他們看見很多賣小吃的店，也有賣衣服和日用品的商店。他們經過兩個小巷子再右轉，這邊的商店比師大路的多。他們逛了半天，白如玉覺得有一點餓，所以他們到一家麵店，點了兩碗牛肉麵。他們一邊吃麵，一邊看著手機裡的地圖，發現離麵店不遠的巷子裡有一家賣背包的店。馬安同正好想買一個背包，所以決定吃了麵就到這家店去看看。最後，馬安同買了一個背包，白如玉也在附近買了兩枝筆和一本本子。馬安同和白如玉都覺得，逛師大附近的店真有意思，吃的東西和日用品也很便宜。</t>
+  </si>
+  <si>
+    <t>Mǎ Āntóng xiàzài le xīn de dìtú dào shǒujī lǐ, tā zhǎo Bái Rúyù gēn tā zài Shīdà fùjìn zǒuzou, shìshi dìtú hǎo yòng bù hǎo yòng. Tāmen kànzhe dìtú, cóng xuéxiào ménkǒu wǎng zuǒ zhuǎn, guò le Hépíng Dōng Lù jiù dào le Shīdà Lù. Zài Shīdà Lù shàng, tāmen kànjiàn hěn duō mài xiǎochī de diàn, yě yǒu mài yīfú hé rìyòngpǐn de shāngdiàn. Tāmen jīngguò liǎng gè xiǎo xiàngzi zài yòu zhuǎn, zhè biān de shāngdiàn bǐ Shīdà Lù de duō. Tāmen guàng le bàn tiān, Bái Rúyù juéde yǒu yìdiǎn è, suǒyǐ tāmen dào yì jiā miàn diàn, diǎn le liǎng wǎn niúròu miàn. Tāmen yìbiān chī miàn, yìbiān kànzhe shǒujī lǐ de dìtú, fāxiàn lí miàn diàn bù yuǎn de xiàngzi lǐ yǒu yì jiā mài bèibāo de diàn. Mǎ Āntóng zhènghǎo xiǎng mǎi yí gè bèibāo, suǒyǐ juédìng chī le miàn jiù dào zhè jiā diàn qù kànkan. Zuìhòu, Mǎ Āntóng mǎi le yí gè bèibāo, Bái Rúyù yě zài fùjìn mǎi le liǎng zhī bǐ hé yì běn běnzi. Mǎ Āntóng hé Bái Rúyù dōu juéde, guàng Shīdà fùjìn de diàn zhēn yǒu yìsi, chī de dōngxi hé rìyòngpǐn yě hěn piányí.</t>
+  </si>
+  <si>
+    <t>Ruyu: Good morning, Antong! Where are you going? Antong: Morning! I made plans with a friend to go watch a movie. What about you? Ruyu: I’m going to see a computer exhibition. Antong: Where are you going to see the computer exhibition? Ruyu: At the World Trade Exhibition Hall. I’m going to take the bus across the street now. Antong: That place is not far from Taipei 101. Why don’t you take the MRT? Ruyu: My friend told me the bus goes directly to the exhibition hall, so I don’t need to transfer. Antong: Taking the MRT is also very convenient. You can take Line 2 to Taipei Main Station, then transfer to the exhibition hall. Ruyu: It sounds like taking the MRT is more troublesome. Antong: Not at all. The MRT is faster; taking the bus takes more than an hour. You should take the MRT! Ruyu: Is the MRT station far? Antong: The MRT station is right ahead. Ruyu: Thank you! I should hurry and go. Antong: Don’t rush, walk slowly. There are many MRT trains. Ruyu: Okay, see you next week.</t>
+  </si>
+  <si>
+    <t>如玉：安同，早！你要去哪裡？安同：早！我約了朋友一起去看電影，你呢？如玉：我要去看電腦展。安同：你去哪裡看電腦展？如玉：世貿展覽館，我現在要去對面坐公車。安同：那裡離台北101不遠，妳怎麼不坐捷運呢？如玉：朋友告訴我公車直接到展覽館，不必換車。安同：坐捷運也很方便。妳先坐2號線到台北車站，再換車到展覽館。如玉：聽起來坐捷運比較麻煩。安同：一點也不麻煩，捷運比較快，坐公車要花一個多小時。你還是坐捷運吧！如玉：捷運站遠嗎？安同：捷運站就在前面。如玉：謝謝！我得趕快走了。安同：別急，走慢一點。捷運的班次很多。如玉：好，我們下禮拜見。</t>
+  </si>
+  <si>
+    <t>Rúyù: Āntóng, zǎo! Nǐ yào qù nǎlǐ? Āntóng: Zǎo! Wǒ yuē le péngyǒu yìqǐ qù kàn diànyǐng, nǐ ne? Rúyù: Wǒ yào qù kàn diànnǎo zhǎn. Āntóng: Nǐ qù nǎlǐ kàn diànnǎo zhǎn? Rúyù: Shìmào Zhǎnlǎn Guǎn, wǒ xiànzài yào qù duìmiàn zuò gōngchē. Āntóng: Nàlǐ lí Táiběi yī líng yī bù yuǎn, nǐ zěnme bù zuò jiéyùn ne? Rúyù: Péngyǒu gàosu wǒ gōngchē zhíjiē dào zhǎnlǎn guǎn, bùbì huànchē. Āntóng: Zuò jiéyùn yě hěn fāngbiàn. Nǐ xiān zuò èr hào xiàn dào Táiběi Chēzhàn, zài huànchē dào zhǎnlǎn guǎn. Rúyù: Tīng qǐlái zuò jiéyùn bǐjiào máfan. Āntóng: Yìdiǎn yě bù máfan, jiéyùn bǐjiào kuài, zuò gōngchē yào huā yí gè duō xiǎoshí. Nǐ háishi zuò jiéyùn ba! Rúyù: Jiéyùn zhàn yuǎn ma? Āntóng: Jiéyùn zhàn jiù zài qiánmiàn. Rúyù: Xièxiè! Wǒ děi gǎnkuài zǒu le. Āntóng: Bié jí, zǒu màn yìdiǎn. Jiéyùn de bāncì hěn duō. Rúyù: Hǎo, wǒmen xià lǐbài jiàn.</t>
+  </si>
+  <si>
+    <t>Ruyu’s friend Meimei came from France to Taiwan for a two-week trip. She first flew from Europe to Vietnam, then transferred to Taiwan. After arriving at the airport, Meimei directly took a bus to Taipei. Ruyu told her that taking the MRT in the city is the most convenient, so after getting off the bus, she took the MRT to her hotel. Meimei felt that transportation in Taipei is very convenient. There are buses, taxis, and the MRT everywhere, making it easy to go anywhere. The MRT routes in Taipei are not complicated, and tickets are not expensive. With an EasyCard, anyone can travel around easily. Meimei lives in eastern France and doesn’t often have the chance to go to the seaside. She heard that the small islands near Taiwan are very beautiful, so she decided to visit Green Island. Green Island is located on the southeast side of Taiwan, and it is not very convenient to get there. Meimei needs to take a train to Taitung first, then take a boat or a plane to Green Island. She plans to go to Green Island in the second week and enjoy her trip.</t>
+  </si>
+  <si>
+    <t>如玉的朋友美美從法國到台灣來玩兩個禮拜，她先從歐洲坐飛機到越南，再轉機到台灣。到了機場，美美直接坐巴士到台北。如玉告訴她，在市區坐捷運是最方便的，所以她下了巴士，就坐捷運到旅館去了。美美覺得台北的交通非常便利，到處都有公車、計程車，還有捷運，去哪裡都很方便。台北捷運的路線不複雜，車票也不貴，買一張悠遊卡，誰都可以輕輕鬆鬆地去逛逛。美美住在法國東部，沒有什麼機會到海邊。聽說台灣附近的小島風景都很美，所以她決定到綠島去看看。綠島在台灣的東南邊，到那裡不太方便。美美得先坐火車到台東，再搭船或是飛機到綠島。她打算第二個星期去綠島，好好地玩一玩。</t>
+  </si>
+  <si>
+    <t>Rúyù de péngyǒu Měiměi cóng Fǎguó dào Táiwān lái wán liǎng gè lǐbài, tā xiān cóng Ōuzhōu zuò fēijī dào Yuènán, zài zhuǎnjī dào Táiwān. Dào le jīchǎng, Měiměi zhíjiē zuò bāshì dào Táiběi. Rúyù gàosu tā, zài shìqū zuò jiéyùn shì zuì fāngbiàn de, suǒyǐ tā xià le bāshì, jiù zuò jiéyùn dào lǚguǎn qù le. Měiměi juéde Táiběi de jiāotōng fēicháng biànlì, dàochù dōu yǒu gōngchē, jìchéngchē, hái yǒu jiéyùn, qù nǎlǐ dōu hěn fāngbiàn. Táiběi jiéyùn de lùxiàn bù fùzá, chēpiào yě bù guì, mǎi yì zhāng Yōuyóukǎ, shuí dōu kěyǐ qīngqīngsōngsōng de qù guàngguang. Měiměi zhù zài Fǎguó dōngbù, méiyǒu shénme jīhuì dào hǎibiān. Tīngshuō Táiwān fùjìn de xiǎodǎo fēngjǐng dōu hěn měi, suǒyǐ tā juédìng dào Lǜdǎo qù kànkan. Lǜdǎo zài Táiwān de dōngnán biān, dào nàlǐ bù tài fāngbiàn. Měiměi děi xiān zuò huǒchē dào Táidōng, zài dā chuán huò shì fēijī dào Lǜdǎo. Tā dǎsuàn dì èr gè xīngqī qù Lǜdǎo, hǎohǎo de wán yì wán.</t>
+  </si>
+  <si>
+    <t>Tianzhong: Good morning, you came very early today. Ruyu: Yes! I came by MRT today. Tianzhong: For today’s exam, are you prepared? Ruyu: I’m almost ready; I should do pretty well. You think listening and writing are easy, right? Tianzhong: Yes, Japanese people start learning to write Chinese characters from elementary school. Ruyu: I also feel writing characters is not difficult now because I already learned them when I was in high school in the U.S. Tianzhong: How long have you studied at this language center? Ruyu: I’ve only studied for half a year. What about you? Tianzhong: I’ve been here for almost a year, but my speaking is still not fluent enough. Ruyu: Although I’ve only been here for half a year, I know my Chinese has improved. Tianzhong: I think learning Chinese in a Chinese-speaking environment improves faster. Ruyu: I agree. I hope I can read Chinese newspapers when I return to my country. Tianzhong: I think you definitely can. After class today, where are you going? Ruyu: I’m going to the activity center to meet friends for language exchange. Tianzhong: Where is the activity center you mentioned? Ruyu: It’s in the building with a bakery on the first floor. We went there once to listen to a lecture, remember? Tianzhong: Oh, I remember now.</t>
+  </si>
+  <si>
+    <t>田中：早，妳今天來得真早。如玉：是啊！我今天是搭捷運來的。田中：今天的考試，妳準備了嗎？如玉：準備得差不多了，應該可以考得不錯。你覺得聽寫很容易吧？田中：是啊，日本人從小學就開始學寫漢字。如玉：我現在也覺得寫字不難，因為我在美國念高中的時候就學過了。田中：妳在這個語言中心學了多久了？如玉：我才學了半年，你呢？田中：我來了快一年了，可是我說話還說得不夠流利。如玉：雖然我只來了半年，但是我知道我的中文進步了。田中：我覺得在說中文的環境裡學中文，進步得比較快。如玉：我同意。我希望回國的時候能看中文報紙。田中：我想妳一定可以。今天下了課，妳要去哪裡？如玉：我要去活動中心跟語言交換的朋友見面。田中：妳說的活動中心在哪裡？如玉：在一樓有麵包店的那棟樓裡面，我們一起去聽過一次演講，記得嗎？田中：哦，我想起來了。</t>
+  </si>
+  <si>
+    <t>Tiánzhōng: Zǎo, nǐ jīntiān lái de zhēn zǎo. Rúyù: Shì a! Wǒ jīntiān shì dā jiéyùn lái de. Tiánzhōng: Jīntiān de kǎoshì, nǐ zhǔnbèi le ma? Rúyù: Zhǔnbèi de chàbùduō le, yīnggāi kěyǐ kǎo de búcuò. Nǐ juéde tīngxiě hěn róngyì ba? Tiánzhōng: Shì a, Rìběn rén cóng xiǎoxué jiù kāishǐ xué xiě Hànzì. Rúyù: Wǒ xiànzài yě juéde xiě zì bù nán, yīnwèi wǒ zài Měiguó niàn gāozhōng de shíhou jiù xué guò le. Tiánzhōng: Nǐ zài zhège yǔyán zhōngxīn xué le duōjiǔ le? Rúyù: Wǒ cái xué le bàn nián, nǐ ne? Tiánzhōng: Wǒ lái le kuài yì nián le, kěshì wǒ shuōhuà hái shuō de bùgòu liúlì. Rúyù: Suīrán wǒ zhǐ lái le bàn nián, dànshì wǒ zhīdào wǒ de Zhōngwén jìnbù le. Tiánzhōng: Wǒ juéde zài shuō Zhōngwén de huánjìng lǐ xué Zhōngwén, jìnbù de bǐjiào kuài. Rúyù: Wǒ tóngyì. Wǒ xīwàng huíguó de shíhou néng kàn Zhōngwén bàozhǐ. Tiánzhōng: Wǒ xiǎng nǐ yídìng kěyǐ. Jīntiān xià le kè, nǐ yào qù nǎlǐ? Rúyù: Wǒ yào qù huódòng zhōngxīn gēn yǔyán jiāohuàn de péngyǒu jiànmiàn. Tiánzhōng: Nǐ shuō de huódòng zhōngxīn zài nǎlǐ? Rúyù: Zài yì lóu yǒu miànbāo diàn de nà dòng lóu lǐmiàn, wǒmen yìqǐ qù tīng guò yí cì yǎnjiǎng, jìde ma? Tiánzhōng: Ò, wǒ xiǎng qǐlái le.</t>
+  </si>
+  <si>
+    <t>Ma Antong came to NTNU to learn Chinese. He chose to take three hours of classes every day. After class, he has to do homework and prepare for the next day’s lessons. When he first started learning to write Chinese characters, he felt it was very difficult, so he practiced writing every day and often didn’t go to sleep until after midnight. Although he was a bit tired, he was very happy that he can now write many characters. On weekends, Ma Antong is more relaxed than usual. Sometimes he takes the MRT to Maokong to drink tea, and sometimes he takes a bus to Yangmingshan to hike. While hiking, he met many Taiwanese people. Taiwanese people are very friendly to foreigners; they often chat with him and tell him about Taiwanese culture. Ma Antong has a language exchange friend. Whenever they have free time, they take a map and ride the MRT to walk around. Antong likes to look at advertisements on the MRT; if there are characters he hasn’t learned, he asks his friend how to say them. He feels that walking around allows him to understand Taiwanese life and also practice Chinese. You can learn Chinese anywhere—it’s really great.</t>
+  </si>
+  <si>
+    <t>馬安同到師大來學中文，他選了每天上三個小時的課，下了課要寫作業，還要準備第二天的課。馬安同剛開始學寫中國字，覺得真難，所以每天都練習寫字，常常半夜十二點多才睡覺。雖然有點累，但是他很高興現在會寫很多字了。週末，馬安同比平常輕鬆多了。他有時候搭捷運去貓空喝茶，有時候坐公車去陽明山爬山。爬山的時候，他認識了很多台灣人。台灣人對外國人很好，常常跟馬安同聊天，告訴他一些台灣的文化。馬安同有一個語言交換的朋友，他們一有空，就拿著地圖搭捷運去逛逛。安同喜歡看捷運上的廣告，要是有沒學過的字，他就會問那位朋友怎麼說。他覺得到處走走，可以了解台灣人的生活，也可以練習練習中文，哪裡都能學中文，真是不錯。</t>
+  </si>
+  <si>
+    <t>Mǎ Āntóng dào Shīdà lái xué Zhōngwén, tā xuǎn le měitiān shàng sān gè xiǎoshí de kè, xià le kè yào xiě zuòyè, hái yào zhǔnbèi dì èr tiān de kè. Mǎ Āntóng gāng kāishǐ xué xiě Zhōngguó zì, juéde zhēn nán, suǒyǐ měitiān dōu liànxí xiě zì, chángcháng bànyè shí’èr diǎn duō cái shuìjiào. Suīrán yǒudiǎn lèi, dànshì tā hěn gāoxìng xiànzài huì xiě hěn duō zì le. Zhōumò, Mǎ Āntóng bǐ píngcháng qīngsōng duō le. Tā yǒu shíhou dā jiéyùn qù Māokōng hē chá, yǒu shíhou zuò gōngchē qù Yángmíngshān páshān. Páshān de shíhou, tā rènshi le hěn duō Táiwān rén. Táiwān rén duì wàiguó rén hěn hǎo, chángcháng gēn Mǎ Āntóng liáotiān, gàosu tā yìxiē Táiwān de wénhuà. Mǎ Āntóng yǒu yí gè yǔyán jiāohuàn de péngyǒu, tāmen yí yǒu kòng, jiù názhe dìtú dā jiéyùn qù guàngguang. Āntóng xǐhuān kàn jiéyùn shàng de guǎnggào, yàoshi yǒu méi xué guò de zì, tā jiù huì wèn nà wèi péngyǒu zěnme shuō. Tā juéde dàochù zǒuzou, kěyǐ liǎojiě Táiwān rén de shēnghuó, yě kěyǐ liànxí liànxí Zhōngwén, nǎlǐ dōu néng xué Zhōngwén, zhēn shì búcuò.</t>
+  </si>
+  <si>
+    <t>Director: Please sit. Are you Gao Meiling? Meiling: Yes. Hello. Director: Please introduce yourself first. Meiling: My name is Gao Meiling. I’m French. I’m 28 years old this year, and I’m currently studying Chinese at NTNU. When I was in university, I studied Asian culture and linguistics. Director: Do you have any experience teaching French? Please tell me about it. Meiling: Yes. I worked as a language assistant before, and at that time all my students were foreigners. Director: How many days a week can you work? Meiling: I study Chinese in the morning now. After 2 PM, I’m available, but I hope to teach only three days a week. Director: Besides French and Chinese, what other languages can you speak? Meiling: I can also speak Spanish and English. Director: Have you taught Spanish before? Meiling: During the summer of my third year in university, I worked as a Spanish teacher. Director: Your work experience sounds very good. Meiling: Thank you. By the way, may I ask how the salary is calculated at your center? Director: We calculate pay based on university professor hourly rates. The salary is the same as university teachers. Meiling: I would really like to try this job. Director: Welcome. Can you start from the first of next month? Meiling: Yes, I can. Thank you.</t>
+  </si>
+  <si>
+    <t>主任：請坐，妳是高美玲嗎？美玲：是。您好。主任：請妳先介紹一下自己。美玲：我叫高美玲，是法國人，今年二十八歲，現在在師大學中文。我念大學的時候上過亞洲文化和語言學。主任：妳有沒有教法文的經驗？請妳談一談。美玲：有。我當過語言助教，那時候的學生都是外國人。主任：妳一個星期能來幾天？美玲：我現在上午學中文，下午兩點以後都可以，但是我希望一個禮拜教三天就好了。主任：妳除了法文、中文，還會什麼語言？美玲：我還會說西班牙語和英文。主任：妳教過西班牙語嗎？美玲：我大學三年級的暑假，當過西班牙語老師。主任：妳的工作經驗聽起來很不錯。美玲：謝謝您。對了，我想請教一下，貴中心老師的薪水怎麼算？主任：我們是按照大學教授的鐘點費算的。薪水跟大學老師的一樣。美玲：我很想試試這份工作。主任：歡迎妳，妳下個月一號就可以來嗎？美玲：可以的。謝謝。</t>
+  </si>
+  <si>
+    <t>Zhǔrèn: Qǐng zuò, nǐ shì Gāo Měilíng ma? Měilíng: Shì. Nín hǎo. Zhǔrèn: Qǐng nǐ xiān jièshào yíxià zìjǐ. Měilíng: Wǒ jiào Gāo Měilíng, shì Fǎguó rén, jīnnián èrshíbā suì, xiànzài zài Shīdà xué Zhōngwén. Wǒ niàn dàxué de shíhou shàng guò Yàzhōu wénhuà hé yǔyánxué. Zhǔrèn: Nǐ yǒu méiyǒu jiāo Fǎwén de jīngyàn? Qǐng nǐ tán yì tán. Měilíng: Yǒu. Wǒ dāng guò yǔyán zhùjiào, nà shíhou de xuéshēng dōu shì wàiguó rén. Zhǔrèn: Nǐ yí gè xīngqī néng lái jǐ tiān? Měilíng: Wǒ xiànzài shàngwǔ xué Zhōngwén, xiàwǔ liǎng diǎn yǐhòu dōu kěyǐ, dànshì wǒ xīwàng yí gè lǐbài jiāo sān tiān jiù hǎo le. Zhǔrèn: Nǐ chúle Fǎwén, Zhōngwén, hái huì shénme yǔyán? Měilíng: Wǒ hái huì shuō Xībānyá yǔ hé Yīngwén. Zhǔrèn: Nǐ jiāo guò Xībānyá yǔ ma? Měilíng: Wǒ dàxué sān niánjí de shǔjià, dāng guò Xībānyá yǔ lǎoshī. Zhǔrèn: Nǐ de gōngzuò jīngyàn tīng qǐlái hěn búcuò. Měilíng: Xièxiè nín. Duì le, wǒ xiǎng qǐngjiào yíxià, guì zhōngxīn lǎoshī de xīnshuǐ zěnme suàn? Zhǔrèn: Wǒmen shì ànzhào dàxué jiàoshòu de zhōngdiǎn fèi suàn de. Xīnshuǐ gēn dàxué lǎoshī de yíyàng. Měilíng: Wǒ hěn xiǎng shìshi zhè fèn gōngzuò. Zhǔrèn: Huānyíng nǐ, nǐ xià gè yuè yī hào jiù kěyǐ lái ma? Měilíng: Kěyǐ de. Xièxiè.</t>
+  </si>
+  <si>
+    <t>Gao Meiling has been in Taiwan for a year. According to Taiwan’s laws, she is already allowed to work, so her Taiwanese friend introduced her to a job teaching French at a university language center. Although Gao Meiling felt that her experience was not enough, she decided to give it a try. So she took her resume to the language center for an interview with the director. The director’s surname is Huang; he is a French-Chinese and has lived in Taiwan for more than ten years. He has also worked at a university for over ten years. When Gao Meiling talked with him in the office, he first asked about her work experience in France, and then asked about her situation learning Chinese and living in Taiwan. Director Huang felt that Gao Meiling’s experience was very suitable for the job. He also introduced the teaching materials to Gao Meiling and explained the working environment to her. Then he told her that the salary would be calculated based on working hours and paid at the end of each month. Gao Meiling felt that this job sounded very good, so she immediately accepted it. Director Huang told her that she could start work on the first of next month. Gao Meiling did not expect the interview to go so smoothly.</t>
+  </si>
+  <si>
+    <t>高美玲來了一年了，按照台灣的法律，她已經可以打工了，所以她的台灣朋友給她介紹了一個在大學語言中心教法文的工作。雖然高美玲覺得自己的經驗還不夠，可是決定去試一試。所以她帶著履歷表到語言中心去跟主任面談。這位主任姓黃，是法國華僑，在台灣住了十幾年，他也在大學工作了十年了。高美玲在辦公室跟他談話的時候，他先問高美玲在法國的工作經驗，再問她在台灣學中文跟生活的情形。黃主任覺得高美玲的經驗很適合這份工作。他也給高美玲介紹了上課的書，還跟她說明了工作環境。然後，黃主任告訴高美玲，薪水按照工作的時間算，每個月的月底發薪水。高美玲覺得這份工作聽起來很不錯，所以馬上就答應了。黃主任對她說，下個月一號就開始上班。高美玲沒想到這次的面談這麼順利。</t>
+  </si>
+  <si>
+    <t>Gāo Měilíng lái le yì nián le, ànzhào Táiwān de fǎlǜ, tā yǐjīng kěyǐ dǎgōng le, suǒyǐ tā de Táiwān péngyǒu gěi tā jièshào le yí gè zài dàxué yǔyán zhōngxīn jiāo Fǎwén de gōngzuò. Suīrán Gāo Měilíng juéde zìjǐ de jīngyàn hái bùgòu, kěshì juédìng qù shì yí shì. Suǒyǐ tā dài zhe lǚlì biǎo dào yǔyán zhōngxīn qù gēn zhǔrèn miàntán. Zhè wèi zhǔrèn xìng Huáng, shì Fǎguó Huáqiáo, zài Táiwān zhù le shí jǐ nián, tā yě zài dàxué gōngzuò le shí nián le. Gāo Měilíng zài bàngōngshì gēn tā tánhuà de shíhou, tā xiān wèn Gāo Měilíng zài Fǎguó de gōngzuò jīngyàn, zài wèn tā zài Táiwān xué Zhōngwén gēn shēnghuó de qíngxíng. Huáng zhǔrèn juéde Gāo Měilíng de jīngyàn hěn shìhé zhè fèn gōngzuò. Tā yě gěi Gāo Měilíng jièshào le shàngkè de shū, hái gēn tā shuōmíng le gōngzuò huánjìng. Ránhòu, Huáng zhǔrèn gàosu Gāo Měilíng, xīnshuǐ ànzhào gōngzuò de shíjiān suàn, měi gè yuè de yuèdǐ fā xīnshuǐ. Gāo Měilíng juéde zhè fèn gōngzuò tīng qǐlái hěn búcuò, suǒyǐ mǎshàng jiù dāyìng le. Huáng zhǔrèn duì tā shuō, xià gè yuè yī hào jiù kāishǐ shàngbān. Gāo Měilíng méi xiǎngdào zhè cì de miàntán zhème shùnlì.</t>
+  </si>
+  <si>
+    <t>Minghua: Antong, you’re here. Antong: Congratulations! Congratulations! Minghua, this is Gao Meiling, whom I often talk to you about. Meiling, this is the bride’s brother, Li Minghua. Meiling: Mr. Li, congratulations! Thank you for inviting us to your sister’s wedding. Minghua: You’re too polite. Antong, you look very handsome in your suit today. Antong: Thank you. You should dress formally when attending a wedding. Meiling: Why haven’t the guests arrived yet? Minghua: It’s only six o’clock now. The wedding starts at 6:30, so there’s still time. Antong: Minghua, who is the person holding a camera? Minghua: He is the groom’s younger brother. Antong: Where is the groom? Minghua: He is standing at the entrance talking with the guests. Antong: Which one? Minghua: The one wearing a white suit. Antong: The groom looks very handsome. Meiling: Look, who is the lady in the red dress talking with the guests? Minghua: That is the groom’s mother. Meiling: She looks so elegant! Why haven’t we seen the bride? Minghua: We’ll see her in a moment. The wedding is about to start. I’ll take you to your seats.</t>
+  </si>
+  <si>
+    <t>明華：安同，你們來了。安同：恭喜！恭喜！明華，這是我常跟你說的高美玲。美玲，他就是新娘的哥哥，李明華。美玲：李先生，恭喜你們！謝謝你請我們來參加你妹妹的婚禮。明華：你太客氣了。安同，你今天穿西裝真好看。安同：謝謝，參加婚禮應該要穿得很正式。美玲：客人怎麼都還沒到？明華：現在才六點，婚禮六點半開始，時間還早。安同：明華，手裡拿著照相機的那個人是誰？明華：他是新郎的弟弟。安同：新郎呢？明華：他在門口站著跟客人說話。安同：哪一個？明華：就是穿著白西裝的那個。安同：新郎看起來好帥。美玲：你看，那邊那位穿著紅色禮服，跟客人說話的太太是誰？明華：那是新郎的媽媽。美玲：她看起來好高興啊！怎麼沒看見新娘呢？明華：等一下你們就會看見她了。婚禮要開始了，我帶你們去你們的座位吧！</t>
+  </si>
+  <si>
+    <t>Mínghuá: Āntóng, nǐmen lái le. Āntóng: Gōngxǐ! Gōngxǐ! Mínghuá, zhè shì wǒ cháng gēn nǐ shuō de Gāo Měilíng. Měilíng, tā jiù shì xīnniáng de gēge, Lǐ Mínghuá. Měilíng: Lǐ xiānshēng, gōngxǐ nǐmen! Xièxiè nǐ qǐng wǒmen lái cānjiā nǐ mèimei de hūnlǐ. Mínghuá: Nǐ tài kèqì le. Āntóng, nǐ jīntiān chuān xīzhuāng zhēn hǎokàn. Āntóng: Xièxiè, cānjiā hūnlǐ yīnggāi yào chuān de hěn zhèngshì. Měilíng: Kèrén zěnme dōu hái méi dào? Mínghuá: Xiànzài cái liù diǎn, hūnlǐ liù diǎn bàn kāishǐ, shíjiān hái zǎo. Āntóng: Mínghuá, shǒu lǐ názhe zhàoxiàngjī de nà gè rén shì shéi? Mínghuá: Tā shì xīnláng de dìdi. Āntóng: Xīnláng ne? Mínghuá: Tā zài ménkǒu zhànzhe gēn kèrén shuōhuà. Āntóng: Nǎ yí gè? Mínghuá: Jiù shì chuānzhe bái xīzhuāng de nà gè. Āntóng: Xīnláng kàn qǐlái hěn shuài. Měilíng: Nǐ kàn, nàbiān nà wèi chuānzhe hóngsè lǐfú, gēn kèrén shuōhuà de tàitai shì shéi? Mínghuá: Nà shì xīnláng de māma. Měilíng: Tā kàn qǐlái hěn gāoxìng a! Zěnme méi kànjiàn xīnniáng ne? Mínghuá: Děng yíxià nǐmen jiù huì kànjiàn tā le. Hūnlǐ yào kāishǐ le, wǒ dài nǐmen qù nǐmen de zuòwèi ba!</t>
+  </si>
+  <si>
+    <t>Li Minghua invited Antong and Meiling to attend his sister’s wedding. This was Antong’s first time attending a wedding banquet. Li Minghua told them that in Taiwan, most people choose a good day to get married and invite relatives and friends to have a meal together. It is both lively and also a way to celebrate the happy occasion. On the day of the banquet, the groom, the bride, and the guests attending the wedding all dress very nicely. Guests usually prepare a red envelope as a gift for the newlyweds. When all the guests arrive, the banquet begins. Everyone sits around a table, and after a while, dishes are served one by one. Some people chat, adults drink alcohol, and children drink soft drinks. The atmosphere is very lively. While everyone is eating, the groom and bride, along with their parents, come to each table to toast. Guests also wish the couple a happy marriage and early children. When the banquet is almost over, the bride changes into another beautiful dress and walks to the door with the groom to thank the guests. At that time, they also take photos with the guests and say a few words of blessing. After all the guests leave, the banquet ends.</t>
+  </si>
+  <si>
+    <t>李明華請安同和美玲去參加他妹妹的婚禮，這是安同他們第一次去吃喜酒。李明華告訴他們，在台灣，要結婚的人大部分都會找一個好日子，請親戚、朋友一起吃飯，熱熱鬧鬧地慶祝這件喜事。請客的那天，新郎、新娘，還有來吃喜酒的客人都穿得漂漂亮亮的。來參加的客人都會準備一個紅包送新人。等客人都到了，喜宴就開始了。大家坐了一會兒，菜就一樣一樣地上著。有人聊天，成年人喝酒，小孩子喝汽水，熱鬧得不得了。大家吃著吃著，新郎、新娘和他們的父母就來敬酒了。客人也會祝新人百年好合、早生貴子。等喜酒吃得差不多了，新娘會換另外一件漂亮的禮服，跟新郎走到門口向大家說謝謝。這個時候他們也會跟大家一起照相，再多說幾句祝福的話。等客人都回去了，喜宴就結束了。</t>
+  </si>
+  <si>
+    <t>Lǐ Mínghuá qǐng Āntóng hé Měilíng qù cānjiā tā mèimei de hūnlǐ, zhè shì Āntóng tāmen dì yī cì qù chī xǐjiǔ. Lǐ Mínghuá gàosu tāmen, zài Táiwān, yào jiéhūn de rén dà bùfèn dōu huì zhǎo yí gè hǎo rìzi, qǐng qīnqī, péngyǒu yìqǐ chīfàn, rèrè-nàonào de qìngzhù zhè jiàn xǐshì. Qǐngkè de nà tiān, xīnláng, xīnniáng, hái yǒu lái chī xǐjiǔ de kèrén dōu chuān de piàopiàoliàngliàng de. Lái cānjiā de kèrén dōu huì zhǔnbèi yí gè hóngbāo sòng xīn rén. Děng kèrén dōu dào le, xǐyàn jiù kāishǐ le. Dàjiā zuò le yíhuìr, cài jiù yíyàng yíyàng de shàng zhe. Yǒurén liáotiān, chéngniánrén hē jiǔ, xiǎoháizi hē qìshuǐ, rènào de bùdéliǎo. Dàjiā chīzhe chīzhe, xīnláng, xīnniáng hé tāmen de fùmǔ jiù lái jìngjiǔ le. Kèrén yě huì zhù xīn rén bǎinián hǎohé, zǎoshēng guìzǐ. Děng xǐjiǔ chī de chàbùduō le, xīnniáng huì huàn lìngwài yí jiàn piàoliang de lǐfú, gēn xīnláng zǒu dào ménkǒu xiàng dàjiā shuō xièxiè. Zhège shíhou tāmen yě huì gēn dàjiā yìqǐ zhàoxiàng, zài duō shuō jǐ jù zhùfú de huà. Děng kèrén dōu huí qù le, xǐyàn jiù jiéshù le.</t>
+  </si>
+  <si>
+    <t>Meiling: What are you doing? Do you want to go to the park by the river to ride a bike? Dongjian: I’m looking for rental housing information online. Meiling: I heard you are planning to move? Dongjian: Yes, I want to find a place closer to school. Meiling: But I remember you only moved here three months ago. Dongjian: Yes, my contract hasn’t expired yet. Luckily, one of my classmates likes this environment and can move here. Meiling: What kind of house do you want to find? Dongjian: First, I want to find a place near the MRT station. Also, a good environment and lighting are very important. Meiling: Aren’t places near MRT stations more expensive? Dongjian: If it’s too expensive, I’ll look elsewhere. There are so many MRT stations; I think I should be able to find something suitable. Meiling: If you move, I’ll lose a friend to practice Chinese with. That’s a pity! Dongjian: I will still come often. I won’t move everything to the new place; I’ll give some things to friends or leave them here for now. Meiling: Then, do you have to pay rent for both places? Dongjian: My classmate will rent this place, so he is willing to help me pay part of the rent. Meiling: Your classmate is really nice! Dongjian: Yes, he is my best friend in Taiwan. Wait a moment, I’ll put the materials in my backpack. Meiling: Take your time, no rush! Later let’s go ride bikes together.</t>
+  </si>
+  <si>
+    <t>美玲：你在做什麼？要不要到河邊的公園去騎騎腳踏車？東健：我正在網站上找租房子的資料。美玲：我聽說你打算搬家？東健：是啊，我想搬到離學校近一點的地方。美玲：可是我記得你三個月以前才搬到這裡的。東健：對，我的合約還沒到期。還好我有一個同學喜歡這個環境，他可以搬到這裡來住。美玲：你想找什麼樣的房子？東健：我先找捷運站附近的房子。還有，環境好、光線好也很重要。美玲：捷運站附近的房子比較貴吧？東健：如果太貴，我再找別的地方。捷運站那麼多，我想應該有合適的。美玲：如果你搬家了，我就少了一個朋友跟我練習中文。好可惜！東健：我會常來啊。我不會把東西都搬到新家，有一些東西，我會送給朋友或是先放在這裡。美玲：那麼，你要付兩邊的房租嗎？東健：這裡的房租當然是我同學付，他還願意幫我付一部分。美玲：你同學真好！東健：是啊！他是我在台灣最好的朋友。妳再等我一下，我把資料放在隨身背裡。美玲：慢慢來，不急！等一會兒我們再去騎腳踏車。</t>
+  </si>
+  <si>
+    <t>Měilíng: Nǐ zài zuò shénme? Yào bú yào dào hébiān de gōngyuán qù qí qí jiǎotàchē? Dōngjiàn: Wǒ zhèngzài wǎngzhàn shàng zhǎo zū fángzi de zīliào. Měilíng: Wǒ tīngshuō nǐ dǎsuàn bānjiā? Dōngjiàn: Shì a, wǒ xiǎng bān dào lí xuéxiào jìn yìdiǎn de dìfāng. Měilíng: Kěshì wǒ jìde nǐ sān gè yuè yǐqián cái bān dào zhèlǐ de. Dōngjiàn: Duì, wǒ de héyuē hái méi dào qī. Hái hǎo wǒ yǒu yí gè tóngxué xǐhuān zhège huánjìng, tā kěyǐ bān dào zhèlǐ lái zhù. Měilíng: Nǐ xiǎng zhǎo shénme yàng de fángzi? Dōngjiàn: Wǒ xiān zhǎo jiéyùn zhàn fùjìn de fángzi. Hái yǒu, huánjìng hǎo, guāngxiàn hǎo yě hěn zhòngyào. Měilíng: Jiéyùn zhàn fùjìn de fángzi bǐjiào guì ba? Dōngjiàn: Rúguǒ tài guì, wǒ zài zhǎo bié de dìfāng. Jiéyùn zhàn nàme duō, wǒ xiǎng yīnggāi yǒu héshì de. Měilíng: Rúguǒ nǐ bānjiā le, wǒ jiù shǎo le yí gè péngyǒu gēn wǒ liànxí Zhōngwén. Hǎo kěxí! Dōngjiàn: Wǒ huì cháng lái a. Wǒ bú huì bǎ dōngxi dōu bān dào xīn jiā, yǒu yìxiē dōngxi, wǒ huì sòng gěi péngyǒu huòshì xiān fàng zài zhèlǐ. Měilíng: Nàme, nǐ yào fù liǎng biān de fángzū ma? Dōngjiàn: Zhèlǐ de fángzū dāngrán shì wǒ tóngxué fù, tā hái yuànyì bāng wǒ fù yí bùfèn. Měilíng: Nǐ tóngxué zhēn hǎo! Dōngjiàn: Shì a! Tā shì wǒ zài Táiwān zuì hǎo de péngyǒu. Nǐ zài děng wǒ yíxià, wǒ bǎ zīliào fàng zài suíshēn bēi lǐ. Měilíng: Mànmàn lái, bú jí! Děng yíhuìr wǒmen zài qù qí jiǎotàchē.</t>
+  </si>
+  <si>
+    <t>Li Dongjian’s rented house is quite far from National Taiwan Normal University. Every day, riding a bicycle to school takes about one hour, which he feels is very inconvenient. So recently, he plans to move. One day, he searched online for a lot of rental information. Li Dongjian most wants to rent a one-bedroom apartment near an MRT station, with a bed, desk, and chairs, and good lighting. The environment should not be too noisy. However, friends in Taiwan say that this kind of apartment is relatively expensive. Li Dongjian thinks that living costs in Taipei are lower than in Seoul. If he spends more time searching, he should be able to find something affordable and suitable. He also thinks that if he lives closer to school, besides spending more time in the library, he can also read books, write assignments, discuss homework with classmates, and participate in campus activities. But his good friend at Taipei Language Center lives far from there, so he will have one less friend to practice Chinese with. Li Dongjian feels a bit reluctant because he plans to leave some unused things here, so he will still come back often to chat with them.</t>
+  </si>
+  <si>
+    <t>李東健租的房子離師大相當遠，每天騎自行車到學校都得花一個小時左右，他覺得很不方便，所以他最近計畫找房子搬家。這一天，他在網站上看了很多租房子的資料。李東健最想在捷運站附近租一間套房，有床、桌子和椅子這些家具，而且房間的光線要好，環境也不要太吵。可是台灣朋友都說，這種套房房租會比較貴。李東健覺得台北的生活費比首爾低，如果多花一點時間找，一定能找到便宜而且合適的。李東健想，如果他搬到學校附近住，除了留在圖書館的時間能長一點，可以念書、寫作業、跟同學討論功課，還可以參加一些學校的活動。不過他的好朋友在台北語文中心住得比較遠，他也覺得少了一個可以練習中文的朋友。李東健覺得有點不捨，因為他打算把一些不常用的東西先留在這裡，所以還會常常來找他們聊天。</t>
+  </si>
+  <si>
+    <t>Lǐ Dōngjiàn zū de fángzi lí Shīdà xiāngdāng yuǎn, měitiān qí zìxíngchē dào xuéxiào dōu děi huā yí gè xiǎoshí zuǒyòu, tā juéde hěn bù fāngbiàn, suǒyǐ tā zuìjìn jìhuà zhǎo fángzi bānjiā. Zhè yì tiān, tā zài wǎngzhàn shàng kàn le hěn duō zū fángzi de zīliào. Lǐ Dōngjiàn zuì xiǎng zài jiéyùn zhàn fùjìn zū yì jiān tàofáng, yǒu chuáng, zhuōzi hé yǐzi zhèxiē jiājù, érqiě fángjiān de guāngxiàn yào hǎo, huánjìng yě bú yào tài chǎo. Kěshì Táiwān péngyǒu dōu shuō, zhè zhǒng tàofáng fángzū huì bǐjiào guì. Lǐ Dōngjiàn juéde Táiběi de shēnghuó fèi bǐ Shǒu’ěr dī, rúguǒ duō huā yìdiǎn shíjiān zhǎo, yídìng néng zhǎodào piányí érqiě héshì de. Lǐ Dōngjiàn xiǎng, rúguǒ tā bān dào xuéxiào fùjìn zhù, chúle liú zài túshūguǎn de shíjiān néng cháng yìdiǎn, kěyǐ niànshū, xiě zuòyè, gēn tóngxué tǎolùn gōngkè, hái kěyǐ cānjiā yìxiē xuéxiào de huódòng. Bùguò tā de hǎo péngyǒu zài Táiběi yǔwén zhōngxīn zhù de bǐjiào yuǎn, tā yě juéde shǎo le yí gè kěyǐ liànxí Zhōngwén de péngyǒu. Lǐ Dōngjiàn juéde yǒudiǎn bùshě, yīnwèi tā dǎsuàn bǎ yìxiē bù cháng yòng de dōngxi xiān liú zài zhèlǐ, suǒyǐ hái huì chángcháng lái zhǎo tāmen liáotiān.</t>
+  </si>
+  <si>
+    <t>Mrs. Chen: Dongjian, are you going out? Dongjian: Yes! The garbage truck is coming soon, I need to quickly go downstairs to throw the trash. Mrs. Chen: Throwing trash? Today is Wednesday, they don’t collect garbage! Dongjian: Really? I thought they collect it every day. Mrs. Chen: No, they don’t collect it every Wednesday and Sunday. Dongjian: Then, can’t I throw out these soda cans and paper cups for recycling? Mrs. Chen: Yes! Dongjian: Why is throwing garbage in Taipei so troublesome? Mrs. Chen: At the beginning, people in Taipei also felt this rule was troublesome, but now everyone is used to it. Dongjian: What’s more troublesome is that I must take the garbage out at 9 p.m., otherwise I can’t throw it away. Mrs. Chen: You’re right. Once, I just came back and the garbage truck arrived. I quickly put down my clothes and ran out to throw the trash. Dongjian: Yes! I often see people rushing out to throw garbage. Mrs. Chen: At night, so many people come out of their homes with garbage and stand together waiting for the garbage truck. Don’t you think it’s interesting? Dongjian: Everyone chats while waiting, it really looks interesting. Mrs. Chen: Although throwing garbage is a bit troublesome, it’s actually not that bad. Dongjian: Then what should I do with this bag of garbage? Mrs. Chen: Take it home and throw it tomorrow!</t>
+  </si>
+  <si>
+    <t>陳太太：東健，要出去啊？東健：是啊！垃圾車快來了，我得趕快下樓去倒垃圾。陳太太：丟垃圾？今天是星期三，不收垃圾啊！東健：真的嗎？我以為天天都收。陳太太：不是，每個星期三和星期天是不收的。東健：那麼，我這些汽水罐和紙杯也不能拿出去回收了嗎？陳太太：是啊！東健：為什麼在台北倒垃圾這麼麻煩？陳太太：剛開始的時候，台北人也覺得這個規定很麻煩，現在大家都習慣了。東健：更麻煩的是，我一定要在晚上九點把垃圾拿出去，要不然就不能倒了。陳太太：你說的對，有一次，我一回來，垃圾車就來了。我馬上放下衣服，跑出去倒垃圾。東健：對啊！我常常看到有人趕去倒垃圾。陳太太：晚上，這麼多人從家裡拿著垃圾走出來，一起站著等垃圾車，你不覺得很有趣嗎？東健：大家常一邊聊天，一邊等，看起來真的很有意思。陳太太：雖然倒垃圾有點麻煩，但是好像也不壞。東健：那麼，我這包垃圾怎麼辦？陳太太：你拿回家去，明天再倒吧！</t>
+  </si>
+  <si>
+    <t>Chén tàitai: Dōngjiàn, yào chūqù a? Dōngjiàn: Shì a! Lājī chē kuài lái le, wǒ děi gǎnkuài xià lóu qù dào lājī. Chén tàitai: Diū lājī? Jīntiān shì xīngqīsān, bù shōu lājī a! Dōngjiàn: Zhēn de ma? Wǒ yǐwéi tiāntiān dōu shōu. Chén tàitai: Bú shì, měi gè xīngqīsān hé xīngqītiān shì bù shōu de. Dōngjiàn: Nàme, wǒ zhèxiē qìshuǐ guàn hé zhǐbēi yě bùnéng ná chūqù huíshōu le ma? Chén tàitai: Shì a! Dōngjiàn: Wèishénme zài Táiběi dào lājī zhème máfan? Chén tàitai: Gāng kāishǐ de shíhòu, Táiběi rén yě juéde zhège guīdìng hěn máfan, xiànzài dàjiā dōu xíguàn le. Dōngjiàn: Gèng máfan de shì, wǒ yídìng yào zài wǎnshàng jiǔ diǎn bǎ lājī ná chūqù, yào bùrán jiù bùnéng dào le. Chén tàitai: Nǐ shuō de duì, yǒu yí cì, wǒ yí huílái, lājī chē jiù lái le. Wǒ mǎshàng fàng xià yīfu, pǎo chūqù dào lājī. Dōngjiàn: Duì a! Wǒ chángcháng kàndào yǒurén gǎn qù dào lājī. Chén tàitai: Wǎnshàng, zhème duō rén cóng jiālǐ názhe lājī zǒu chūlái, yìqǐ zhànzhe děng lājī chē, nǐ bù juéde hěn yǒuqù ma? Dōngjiàn: Dàjiā cháng yìbiān liáotiān, yìbiān děng, kàn qǐlái zhēn de hěn yǒu yìsi. Chén tàitai: Suīrán dào lājī yǒudiǎn máfan, dànshì hǎoxiàng yě bú huài. Dōngjiàn: Nàme, wǒ zhè bāo lājī zěnme bàn? Chén tàitai: Nǐ ná huí jiā qù, míngtiān zài dào ba!</t>
+  </si>
+  <si>
+    <t>On Ma An’s second day in Taiwan, in the evening, he surfed the internet in his room and chatted with his parents about life in Taiwan. He suddenly heard music coming from outside, but didn’t know where it was coming from, which felt a bit strange, so he looked out the window. He saw many people carrying bags walking toward the street corner, and the corner was already crowded. Then he realized it was the sound of the garbage truck’s music. When the garbage truck passed by, everyone walked over and threw their trash into it. When foreigners first arrive in Taipei, they don’t know where to throw garbage or when they can do it. It was only after Ma An came to Taiwan that he realized garbage must be thrown at a fixed time every day. Although it is a bit troublesome, there is no garbage on the streets, which is better for the environment in Taipei. To protect the environment, everyone should sort their garbage. Recyclable items like paper, bottles, and plastic cups should be collected and thrown into recycling bins. Now everyone understands that a clean and tidy city is a progressive city.</t>
+  </si>
+  <si>
+    <t>馬安到台灣的第二天，晚上在房間上網，跟父母聊台灣的生活情形，他忽然聽見外面有音樂的聲音，可是不知道音樂是從哪裡來的，覺得有一點奇怪，所以從窗戶往外看。他看見很多人拿著袋子往路口走，路口已經站了很多人，才知道是垃圾車的音樂。那輛垃圾車一開過來，大家就走過去把手裡的垃圾丟進去。外國人剛到台北，不知道哪裡可以丟垃圾，也不知道什麼時候可以丟垃圾，馬安回了台灣才知道，丟垃圾只在一定的時間，一定的地點。雖然有點麻煩，但是路上沒有垃圾，對台北的環境比較好。為了保護環境，大家都應該做垃圾分類，那些可以再利用的紙、瓶子、塑膠杯都要回收，丟進資源回收桶裡。現在大家都知道，一個乾乾淨淨的城市也是一個進步的城市。</t>
+  </si>
+  <si>
+    <t>Mǎ Ān dào Táiwān de dì èr tiān, wǎnshàng zài fángjiān shàngwǎng, gēn fùmǔ liáo Táiwān de shēnghuó qíngxíng, tā hūrán tīngjiàn wàimiàn yǒu yīnyuè de shēngyīn, kěshì bù zhīdào yīnyuè shì cóng nǎlǐ lái de, juéde yǒu yìdiǎn qíguài, suǒyǐ cóng chuānghù wǎng wài kàn. Tā kànjiàn hěn duō rén názhe dàizi wǎng lùkǒu zǒu, lùkǒu yǐjīng zhàn le hěn duō rén, cái zhīdào shì lājī chē de yīnyuè. Nà liàng lājī chē yì kāi guòlái, dàjiā jiù zǒu guòqù bǎ shǒu lǐ de lājī diū jìnqù. Wàiguórén gāng dào Táiběi, bù zhīdào nǎlǐ kěyǐ diū lājī, yě bù zhīdào shénme shíhòu kěyǐ diū lājī, Mǎ Ān huí le Táiwān cái zhīdào, diū lājī zhǐ zài yídìng de shíjiān, yídìng de dìdiǎn. Suīrán yǒudiǎn máfan, dànshì lù shàng méiyǒu lājī, duì Táiběi de huánjìng bǐjiào hǎo. Wèile bǎohù huánjìng, dàjiā dōu yīnggāi zuò lājī fēnlèi, nàxiē kěyǐ zài lìyòng de zhǐ, píngzi, sùliào bēi dōu yào huíshōu, diū jìn zīyuán huíshōu tǒng lǐ. Xiànzài dàjiā dōu zhīdào, yí gè gānggāng jìngjìng de chéngshì yě shì yí gè jìnbù de chéngshì.</t>
+  </si>
+  <si>
+    <t>Dongjian: An Tong! An Tong! An Tong: Dongjian! Sorry, I didn’t hear you calling me. Dongjian: The music was so loud, no wonder you didn’t hear. An Tong: What’s up? Dongjian: Nothing, I just saw you pushing your bike past the school gate. An Tong: What are you doing this afternoon? Dongjian: I’m going to the gym to exercise. By the way, are you still learning Tai Chi? An Tong: Yes! My master says I have talent, and I’m learning well. Dongjian: Is your master Taiwanese? When he speaks Chinese, can you understand? An Tong: At first I couldn’t understand, but now there’s no problem. Dongjian: Is Tai Chi difficult? How long have you been learning? An Tong: It’s not easy, and I have to wake up very early. I’ve been learning for more than three months, and I’ve only learned a little. Dongjian: But Tai Chi movements look slow and gentle, it should be relaxing. An Tong: Those movements look easy, but at the beginning, I couldn’t even get up in the morning, and my legs hurt so much I couldn’t walk. Dongjian: Then how did you keep going? An Tong: Although it’s tiring, it’s my interest. Dongjian: Are you free this afternoon? Do you want to go exercise with me? An Tong: Sure! I’ll go to the library to read first, then I’ll go exercise with you in the afternoon.</t>
+  </si>
+  <si>
+    <t>東健：安同！安同！安同：東健！對不起，沒聽見你叫我。東健：音樂那麼吵，你當然聽不見。安同：有什麼事嗎？東健：沒事，只是一到學校門口，就看見你推著腳踏車走過來。安同：你下午要做什麼？東健：我要去體育館運動。對了，你現在還在學太極拳嗎？安同：是啊！我的師父說我有天分，學得不錯。東健：你師父是台灣人吧？他說中文你聽得懂嗎？安同：剛開始我都聽不懂，可是現在沒問題了。東健：太極拳難嗎？你學了多久了？安同：不太容易，而且要很早起來。我學了三個多月了，才學會了一點。東健：可是太極拳的動作看起來慢慢的，輕輕的，應該很輕鬆。安同：那些動作好像很容易，但是剛開始的時候，我早上常常起不來，腿也痛得走不了路。東健：那你怎麼還學得下去？安同：雖然很累，可是這是我的興趣。東健：你下午沒事吧？要不要跟我一起去運動？安同：好啊！我先去圖書館借書，下午再跟你去運動。</t>
+  </si>
+  <si>
+    <t>Dōngjiàn: Ān Tóng! Ān Tóng! Ān Tóng: Dōngjiàn! Duìbuqǐ, méi tīngjiàn nǐ jiào wǒ. Dōngjiàn: Yīnyuè nàme chǎo, nǐ dāngrán tīng bú jiàn. Ān Tóng: Yǒu shénme shì ma? Dōngjiàn: Méi shì, zhǐshì yí dào xuéxiào ménkǒu, jiù kànjiàn nǐ tuīzhe jiǎotàchē zǒu guòlái. Ān Tóng: Nǐ xiàwǔ yào zuò shénme? Dōngjiàn: Wǒ yào qù tǐyùguǎn yùndòng. Duì le, nǐ xiànzài hái zài xué Tàijíquán ma? Ān Tóng: Shì a! Wǒ de shīfù shuō wǒ yǒu tiānfèn, xué de búcuò. Dōngjiàn: Nǐ shīfù shì Táiwān rén ba? Tā shuō Zhōngwén nǐ tīng de dǒng ma? Ān Tóng: Gāng kāishǐ wǒ dōu tīng bù dǒng, kěshì xiànzài méi wèntí le. Dōngjiàn: Tàijíquán nán ma? Nǐ xué le duō jiǔ le? Ān Tóng: Bù tài róngyì, érqiě yào hěn zǎo qǐlái. Wǒ xué le sān gè duō yuè le, cái xuéhuì le yìdiǎn. Dōngjiàn: Kěshì Tàijíquán de dòngzuò kàn qǐlái màn màn de, qīng qīng de, yīnggāi hěn qīngsōng. Ān Tóng: Nàxiē dòngzuò hǎoxiàng hěn róngyì, dànshì gāng kāishǐ de shíhòu, wǒ zǎoshàng chángcháng qǐ bù lái, tuǐ yě tòng de zǒu bù liǎo lù. Dōngjiàn: Nà nǐ zěnme hái xué de xiàqù? Ān Tóng: Suīrán hěn lèi, kěshì zhè shì wǒ de xìngqù. Dōngjiàn: Nǐ xiàwǔ méi shì ba? Yào bú yào gēn wǒ yìqǐ qù yùndòng? Ān Tóng: Hǎo a! Wǒ xiān qù túshūguǎn jiè shū, xiàwǔ zài gēn nǐ qù yùndòng.</t>
+  </si>
+  <si>
+    <t>Today, when Li Dongjian and Ma An were exercising at the gym, An Tong kept telling him about the benefits of learning Tai Chi and asked whether he was interested. He also said that next time he practices, he could take him along. Dongjian remembered that when An Tong had just started learning kung fu, he often complained. Before every practice, the master required everyone to run one kilometer, and An Tong was always the last to finish, sometimes even unable to complete it. Now, Dongjian noticed that An Tong’s physical strength has improved a lot compared to three months ago. Every morning, An Tong wakes up early to practice. Dongjian originally thought that learning kung fu would take a lot of time and that An Tong might not have time to study. However, to make time for practice, An Tong studies and does homework after class every day, and only practices after finishing his work. Although he spends quite a lot of time practicing, it has not affected his academic performance at all. After seeing that Ma An improved his health and academic performance after learning Tai Chi, Dongjian felt that there are many benefits to practicing Tai Chi, so he decided to tell An Tong tomorrow that he also wants to learn Tai Chi.</t>
+  </si>
+  <si>
+    <t>今天李東健跟馬安同在體育館運動的時候，安同一直跟他說學太極拳的好處，還問他有沒有興趣，下次練習的時候可以帶他一起去。東健想起安同剛開始學功夫的時候，常跟他抱怨，師父每次練習以前，都要大家先跑一千公尺，安同總是最後一個跑完，有的時候還跑不完。現在，東健發現安同的體力比三個月以前好多了，每天早上，安同還是很有精神。李東健本來以為學功夫要花很多時間，安同可能沒有時間念書了，但是安同為了多練習，每天下課，就回宿舍念書、做功課，做完了功課，再去練習。雖然練習的時間不少，但是一點都沒有影響安同的成績。李東健看馬安同學了太極拳以後，身體健康了，功課也進步了，覺得練太極拳的好處真不少，決定明天就跟安同說他也要學太極拳。</t>
+  </si>
+  <si>
+    <t>Jīntiān Lǐ Dōngjiàn gēn Mǎ Ān Tóng zài tǐyùguǎn yùndòng de shíhòu, Ān Tóng yìzhí gēn tā shuō xué Tàijíquán de hǎochù, hái wèn tā yǒu méiyǒu xìngqù, xià cì liànxí de shíhòu kěyǐ dài tā yìqǐ qù. Dōngjiàn xiǎng qǐ Ān Tóng gāng kāishǐ xué gōngfū de shíhòu, cháng gēn tā bàoyuàn, shīfù měi cì liànxí yǐqián, dōu yào dàjiā xiān pǎo yìqiān gōngchǐ, Ān Tóng zǒng shì zuìhòu yí gè pǎo wán, yǒu de shíhòu hái pǎo bù wán. Xiànzài, Dōngjiàn fāxiàn Ān Tóng de tǐlì bǐ sān gè yuè yǐqián hǎo duō le, měitiān zǎoshàng, Ān Tóng hái shì hěn yǒu jīngshén. Lǐ Dōngjiàn běnlái yǐwéi xué gōngfū yào huā hěn duō shíjiān, Ān Tóng kěnéng méiyǒu shíjiān niànshū le, dànshì Ān Tóng wèile duō liànxí, měitiān xiàkè, jiù huí sùshè niànshū, zuò gōngkè, zuò wán le gōngkè, zài qù liànxí. Suīrán liànxí de shíjiān bù shǎo, dànshì yìdiǎn dōu méiyǒu yǐngxiǎng Ān Tóng de chéngjī. Lǐ Dōngjiàn kàn Mǎ Ān Tóng xué le Tàijíquán yǐhòu, shēntǐ jiànkāng le, gōngkè yě jìnbù le, juéde liàn Tàijíquán de hǎochù zhēn bù shǎo, juédìng míngtiān jiù gēn Ān Tóng shuō tā yě yào xué Tàijíquán.</t>
   </si>
 </sst>
 </file>
@@ -10351,7 +10486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1236"/>
+  <dimension ref="A1:D1251"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.44140625" customWidth="1"/>
@@ -27663,6 +27798,216 @@
         <v>3300</v>
       </c>
     </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1237" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>3303</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>3304</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>3305</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1238" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>3306</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>3307</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>3308</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1239" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>3309</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>3310</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1240" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>3313</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>3314</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1241" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>3315</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>3316</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>3317</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1242" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>3319</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>3320</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1243" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>3321</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>3322</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1244" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>3324</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>3325</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>3326</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1245" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>3328</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1246" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1246" t="s">
+        <v>3330</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>3331</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>3332</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1247" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1247" t="s">
+        <v>3333</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>3334</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>3335</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1248" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1248" t="s">
+        <v>3336</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>3337</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>3338</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1249" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1249" t="s">
+        <v>3339</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>3340</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1250" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1250" t="s">
+        <v>3342</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>3343</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>3344</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1251" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1251" t="s">
+        <v>3345</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>3346</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>3347</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
